--- a/Template/GMT-BB30-SPECIAL_template.xlsx
+++ b/Template/GMT-BB30-SPECIAL_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" firstSheet="15" activeTab="26"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" firstSheet="9" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="NS3602_CP1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <sheet name="NS3611_CP7" sheetId="23" r:id="rId27"/>
     <sheet name="NZ8801_CP1" sheetId="29" r:id="rId28"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="145621" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="997">
   <si>
     <t>Date</t>
   </si>
@@ -3001,6 +3001,51 @@
   </si>
   <si>
     <t>EFT_30_RD_NVR_AnalogTrimCode</t>
+  </si>
+  <si>
+    <t>EST_MR_LP_EN0_BKR_Test</t>
+  </si>
+  <si>
+    <t>EST_VBGVref_PVD_TTR_Trim</t>
+  </si>
+  <si>
+    <t>EST_BGVref_LVR_TTR_Trim</t>
+  </si>
+  <si>
+    <t>EST_VBGVref_LVR_TTR_Trim</t>
+  </si>
+  <si>
+    <t>EST_MR_LP_EN1_BKR_Test</t>
+  </si>
+  <si>
+    <t>User_run_current_test</t>
+  </si>
+  <si>
+    <t>699</t>
+  </si>
+  <si>
+    <t>761</t>
+  </si>
+  <si>
+    <t>762</t>
+  </si>
+  <si>
+    <t>799</t>
+  </si>
+  <si>
+    <t>995</t>
+  </si>
+  <si>
+    <t>996</t>
+  </si>
+  <si>
+    <t>997</t>
+  </si>
+  <si>
+    <t>PASS BIN3</t>
+  </si>
+  <si>
+    <t>EFT_WR_RD_CP7_SP_FLAG_test</t>
   </si>
 </sst>
 </file>
@@ -3227,18 +3272,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3246,6 +3279,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3607,34 +3652,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="17" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -3757,15 +3802,15 @@
       <c r="AX1" s="5">
         <v>42</v>
       </c>
-      <c r="AY1" s="33" t="s">
+      <c r="AY1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="AZ1" s="35" t="s">
+      <c r="AZ1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:52" s="17" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -3895,11 +3940,16 @@
       <c r="AX2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AY2" s="34"/>
+      <c r="AY2" s="30"/>
       <c r="AZ2" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AY1:AY2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="F1:F2"/>
@@ -3907,11 +3957,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3942,34 +3987,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:87" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="12">
@@ -4203,7 +4248,7 @@
       <c r="CI1" s="16"/>
     </row>
     <row r="2" spans="1:87" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -4441,6 +4486,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="CG1:CG2"/>
     <mergeCell ref="CH1:CH2"/>
     <mergeCell ref="F1:F2"/>
@@ -4448,11 +4498,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4483,34 +4528,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:95" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="12">
@@ -4768,7 +4813,7 @@
       <c r="CQ1" s="16"/>
     </row>
     <row r="2" spans="1:95" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -5030,6 +5075,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="CO1:CO2"/>
     <mergeCell ref="CP1:CP2"/>
     <mergeCell ref="F1:F2"/>
@@ -5037,11 +5087,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5051,250 +5096,253 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CA2"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:79" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:80" x14ac:dyDescent="0.15">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12">
+      <c r="K1" s="13">
         <v>5</v>
       </c>
-      <c r="L1" s="12">
+      <c r="L1" s="13">
         <v>502</v>
       </c>
-      <c r="M1" s="12">
+      <c r="M1" s="13">
         <v>503</v>
       </c>
-      <c r="N1" s="12">
+      <c r="N1" s="13">
         <v>504</v>
       </c>
-      <c r="O1" s="12">
+      <c r="O1" s="13">
         <v>505</v>
       </c>
-      <c r="P1" s="12">
+      <c r="P1" s="13">
         <v>506</v>
       </c>
-      <c r="Q1" s="12">
+      <c r="Q1" s="13">
         <v>507</v>
       </c>
-      <c r="R1" s="12">
+      <c r="R1" s="13">
         <v>508</v>
       </c>
-      <c r="S1" s="12">
+      <c r="S1" s="13">
         <v>509</v>
       </c>
-      <c r="T1" s="12">
+      <c r="T1" s="13">
         <v>510</v>
       </c>
-      <c r="U1" s="12">
+      <c r="U1" s="13">
         <v>511</v>
       </c>
-      <c r="V1" s="12">
+      <c r="V1" s="13">
         <v>513</v>
       </c>
-      <c r="W1" s="12">
+      <c r="W1" s="13">
         <v>515</v>
       </c>
-      <c r="X1" s="12">
+      <c r="X1" s="13">
         <v>516</v>
       </c>
-      <c r="Y1" s="12">
+      <c r="Y1" s="13">
         <v>517</v>
       </c>
-      <c r="Z1" s="12">
+      <c r="Z1" s="13">
         <v>518</v>
       </c>
-      <c r="AA1" s="12">
+      <c r="AA1" s="13">
         <v>519</v>
       </c>
-      <c r="AB1" s="12">
+      <c r="AB1" s="13">
         <v>520</v>
       </c>
-      <c r="AC1" s="12">
+      <c r="AC1" s="13">
         <v>521</v>
       </c>
-      <c r="AD1" s="12">
+      <c r="AD1" s="13">
         <v>522</v>
       </c>
-      <c r="AE1" s="12">
+      <c r="AE1" s="13">
         <v>523</v>
       </c>
-      <c r="AF1" s="12">
+      <c r="AF1" s="13">
         <v>524</v>
       </c>
-      <c r="AG1" s="12">
+      <c r="AG1" s="13">
         <v>525</v>
       </c>
-      <c r="AH1" s="12">
+      <c r="AH1" s="13">
         <v>526</v>
       </c>
-      <c r="AI1" s="12">
+      <c r="AI1" s="13">
         <v>527</v>
       </c>
-      <c r="AJ1" s="12">
+      <c r="AJ1" s="13">
         <v>528</v>
       </c>
-      <c r="AK1" s="12">
+      <c r="AK1" s="13">
         <v>529</v>
       </c>
-      <c r="AL1" s="12">
+      <c r="AL1" s="13">
         <v>530</v>
       </c>
-      <c r="AM1" s="12">
+      <c r="AM1" s="13">
         <v>531</v>
       </c>
-      <c r="AN1" s="12">
+      <c r="AN1" s="13">
         <v>532</v>
       </c>
-      <c r="AO1" s="12">
+      <c r="AO1" s="13">
         <v>533</v>
       </c>
-      <c r="AP1" s="12">
+      <c r="AP1" s="13">
         <v>534</v>
       </c>
-      <c r="AQ1" s="12">
+      <c r="AQ1" s="13">
         <v>535</v>
       </c>
-      <c r="AR1" s="12">
+      <c r="AR1" s="13">
         <v>536</v>
       </c>
-      <c r="AS1" s="12">
+      <c r="AS1" s="13">
         <v>537</v>
       </c>
-      <c r="AT1" s="12">
+      <c r="AT1" s="13">
         <v>538</v>
       </c>
-      <c r="AU1" s="12">
+      <c r="AU1" s="13">
         <v>539</v>
       </c>
-      <c r="AV1" s="12">
+      <c r="AV1" s="13">
         <v>540</v>
       </c>
-      <c r="AW1" s="12">
+      <c r="AW1" s="13">
         <v>541</v>
       </c>
-      <c r="AX1" s="12">
+      <c r="AX1" s="13">
         <v>542</v>
       </c>
-      <c r="AY1" s="12">
+      <c r="AY1" s="13">
         <v>543</v>
       </c>
-      <c r="AZ1" s="12">
+      <c r="AZ1" s="13">
         <v>544</v>
       </c>
-      <c r="BA1" s="12">
+      <c r="BA1" s="13">
         <v>545</v>
       </c>
-      <c r="BB1" s="12">
+      <c r="BB1" s="13">
+        <v>546</v>
+      </c>
+      <c r="BC1" s="13">
         <v>549</v>
       </c>
-      <c r="BC1" s="12">
-        <v>550</v>
-      </c>
-      <c r="BD1" s="12">
+      <c r="BD1" s="13">
         <v>551</v>
       </c>
-      <c r="BE1" s="12">
+      <c r="BE1" s="13">
         <v>554</v>
       </c>
-      <c r="BF1" s="12">
+      <c r="BF1" s="13">
         <v>555</v>
       </c>
-      <c r="BG1" s="12">
+      <c r="BG1" s="13">
         <v>556</v>
       </c>
-      <c r="BH1" s="12">
+      <c r="BH1" s="13">
         <v>557</v>
       </c>
-      <c r="BI1" s="12">
+      <c r="BI1" s="13">
         <v>558</v>
       </c>
-      <c r="BJ1" s="12">
+      <c r="BJ1" s="13">
         <v>560</v>
       </c>
-      <c r="BK1" s="12">
+      <c r="BK1" s="13">
         <v>570</v>
       </c>
-      <c r="BL1" s="12">
+      <c r="BL1" s="13">
         <v>580</v>
       </c>
-      <c r="BM1" s="12">
+      <c r="BM1" s="13">
         <v>590</v>
       </c>
-      <c r="BN1" s="12">
+      <c r="BN1" s="13">
         <v>590</v>
       </c>
-      <c r="BO1" s="12">
+      <c r="BO1" s="13">
         <v>591</v>
       </c>
-      <c r="BP1" s="12">
+      <c r="BP1" s="13">
         <v>592</v>
       </c>
-      <c r="BQ1" s="12">
+      <c r="BQ1" s="13">
         <v>593</v>
       </c>
-      <c r="BR1" s="12">
+      <c r="BR1" s="13">
         <v>594</v>
       </c>
-      <c r="BS1" s="12">
+      <c r="BS1" s="13">
         <v>595</v>
       </c>
-      <c r="BT1" s="12">
+      <c r="BT1" s="13">
         <v>596</v>
       </c>
-      <c r="BU1" s="12">
+      <c r="BU1" s="13">
         <v>597</v>
       </c>
-      <c r="BV1" s="12">
+      <c r="BV1" s="13">
         <v>598</v>
       </c>
-      <c r="BW1" s="12">
+      <c r="BW1" s="13">
+        <v>599</v>
+      </c>
+      <c r="BX1" s="13">
         <v>995</v>
       </c>
-      <c r="BX1" s="13">
+      <c r="BY1" s="13">
         <v>63</v>
       </c>
-      <c r="BY1" s="12">
+      <c r="BZ1" s="13">
         <v>998</v>
       </c>
-      <c r="BZ1" s="40" t="s">
+      <c r="CA1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="CA1" s="42" t="s">
+      <c r="CB1" s="42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:79" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+    <row r="2" spans="1:80" x14ac:dyDescent="0.15">
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -5304,224 +5352,227 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P2" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q2" s="12" t="s">
+      <c r="P2" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q2" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="U2" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="V2" s="12" t="s">
+      <c r="U2" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="V2" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AA2" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AB2" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AC2" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AD2" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AE2" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="AF2" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AF2" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="AG2" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AH2" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AI2" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AJ2" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AK2" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AL2" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AM2" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AN2" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="AO2" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="AP2" s="12" t="s">
+      <c r="AP2" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="AQ2" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="AR2" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="AS2" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="AT2" s="12" t="s">
+      <c r="AQ2" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="AS2" s="13" t="s">
+        <v>985</v>
+      </c>
+      <c r="AT2" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AU2" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="AV2" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="AW2" s="12" t="s">
+      <c r="AW2" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="AX2" s="12" t="s">
+      <c r="AX2" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="AY2" s="12" t="s">
+      <c r="AY2" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="AZ2" s="12" t="s">
+      <c r="AZ2" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="BA2" s="12" t="s">
+      <c r="BA2" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="BB2" s="12" t="s">
+      <c r="BB2" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="BC2" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="BC2" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="BD2" s="12" t="s">
+      <c r="BD2" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="BE2" s="12" t="s">
+      <c r="BE2" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="BF2" s="12" t="s">
+      <c r="BF2" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="BG2" s="12" t="s">
+      <c r="BG2" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="BH2" s="12" t="s">
+      <c r="BH2" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="BI2" s="12" t="s">
+      <c r="BI2" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="BJ2" s="12" t="s">
+      <c r="BJ2" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="BK2" s="12" t="s">
+      <c r="BK2" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="BL2" s="12" t="s">
+      <c r="BL2" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="BM2" s="12" t="s">
+      <c r="BM2" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="BN2" s="12" t="s">
+      <c r="BN2" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="BO2" s="12" t="s">
+      <c r="BO2" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="BP2" s="12" t="s">
+      <c r="BP2" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="BQ2" s="12" t="s">
+      <c r="BQ2" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="BR2" s="12" t="s">
+      <c r="BR2" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="BS2" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="BT2" s="12" t="s">
+      <c r="BT2" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="BU2" s="12" t="s">
+      <c r="BU2" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="BV2" s="12" t="s">
+      <c r="BV2" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="BW2" s="12" t="s">
+      <c r="BW2" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="BX2" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="BX2" s="13" t="s">
+      <c r="BY2" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="BY2" s="12" t="s">
+      <c r="BZ2" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="BZ2" s="41"/>
-      <c r="CA2" s="43"/>
+      <c r="CA2" s="41"/>
+      <c r="CB2" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="BZ1:BZ2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="CB1:CB2"/>
     <mergeCell ref="CA1:CA2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5530,385 +5581,391 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DT2"/>
+  <dimension ref="A1:DV2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:126" x14ac:dyDescent="0.15">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12">
+      <c r="K1" s="13">
         <v>6</v>
       </c>
-      <c r="L1" s="12">
+      <c r="L1" s="13">
         <v>502</v>
       </c>
-      <c r="M1" s="12">
+      <c r="M1" s="13">
         <v>503</v>
       </c>
-      <c r="N1" s="12">
+      <c r="N1" s="13">
         <v>504</v>
       </c>
-      <c r="O1" s="12">
+      <c r="O1" s="13">
         <v>505</v>
       </c>
-      <c r="P1" s="12">
+      <c r="P1" s="13">
         <v>506</v>
       </c>
-      <c r="Q1" s="12">
+      <c r="Q1" s="13">
         <v>507</v>
       </c>
-      <c r="R1" s="12">
+      <c r="R1" s="13">
         <v>508</v>
       </c>
-      <c r="S1" s="12">
+      <c r="S1" s="13">
         <v>509</v>
       </c>
-      <c r="T1" s="12">
+      <c r="T1" s="13">
         <v>510</v>
       </c>
-      <c r="U1" s="12">
+      <c r="U1" s="13">
         <v>511</v>
       </c>
-      <c r="V1" s="12">
+      <c r="V1" s="13">
         <v>513</v>
       </c>
-      <c r="W1" s="12">
+      <c r="W1" s="13">
         <v>515</v>
       </c>
-      <c r="X1" s="12">
+      <c r="X1" s="13">
         <v>516</v>
       </c>
-      <c r="Y1" s="12">
+      <c r="Y1" s="13">
         <v>517</v>
       </c>
-      <c r="Z1" s="12">
+      <c r="Z1" s="13">
         <v>518</v>
       </c>
-      <c r="AA1" s="12">
+      <c r="AA1" s="13">
         <v>519</v>
       </c>
-      <c r="AB1" s="12">
+      <c r="AB1" s="13">
         <v>520</v>
       </c>
-      <c r="AC1" s="12">
+      <c r="AC1" s="13">
         <v>521</v>
       </c>
-      <c r="AD1" s="12">
+      <c r="AD1" s="13">
         <v>522</v>
       </c>
-      <c r="AE1" s="12">
+      <c r="AE1" s="13">
         <v>523</v>
       </c>
-      <c r="AF1" s="12">
+      <c r="AF1" s="13">
         <v>524</v>
       </c>
-      <c r="AG1" s="12">
+      <c r="AG1" s="13">
         <v>525</v>
       </c>
-      <c r="AH1" s="12">
+      <c r="AH1" s="13">
         <v>526</v>
       </c>
-      <c r="AI1" s="12">
+      <c r="AI1" s="13">
         <v>527</v>
       </c>
-      <c r="AJ1" s="12">
+      <c r="AJ1" s="13">
         <v>528</v>
       </c>
-      <c r="AK1" s="12">
+      <c r="AK1" s="13">
         <v>529</v>
       </c>
-      <c r="AL1" s="12">
+      <c r="AL1" s="13">
         <v>530</v>
       </c>
-      <c r="AM1" s="12">
+      <c r="AM1" s="13">
         <v>531</v>
       </c>
-      <c r="AN1" s="12">
+      <c r="AN1" s="13">
         <v>532</v>
       </c>
-      <c r="AO1" s="12">
+      <c r="AO1" s="13">
         <v>533</v>
       </c>
-      <c r="AP1" s="12">
+      <c r="AP1" s="13">
         <v>534</v>
       </c>
-      <c r="AQ1" s="12">
+      <c r="AQ1" s="13">
         <v>535</v>
       </c>
-      <c r="AR1" s="12">
+      <c r="AR1" s="13">
         <v>536</v>
       </c>
-      <c r="AS1" s="12">
+      <c r="AS1" s="13">
         <v>537</v>
       </c>
-      <c r="AT1" s="12">
+      <c r="AT1" s="13">
         <v>538</v>
       </c>
-      <c r="AU1" s="12">
+      <c r="AU1" s="13">
         <v>539</v>
       </c>
-      <c r="AV1" s="12">
+      <c r="AV1" s="13">
         <v>540</v>
       </c>
-      <c r="AW1" s="12">
+      <c r="AW1" s="13">
         <v>541</v>
       </c>
-      <c r="AX1" s="12">
+      <c r="AX1" s="13">
         <v>542</v>
       </c>
-      <c r="AY1" s="12">
+      <c r="AY1" s="13">
         <v>543</v>
       </c>
-      <c r="AZ1" s="12">
+      <c r="AZ1" s="13">
         <v>544</v>
       </c>
-      <c r="BA1" s="12">
+      <c r="BA1" s="13">
         <v>545</v>
       </c>
-      <c r="BB1" s="12">
+      <c r="BB1" s="13">
+        <v>546</v>
+      </c>
+      <c r="BC1" s="13">
         <v>549</v>
       </c>
-      <c r="BC1" s="12">
-        <v>550</v>
-      </c>
-      <c r="BD1" s="12">
+      <c r="BD1" s="13">
         <v>551</v>
       </c>
-      <c r="BE1" s="12">
+      <c r="BE1" s="13">
         <v>554</v>
       </c>
-      <c r="BF1" s="12">
+      <c r="BF1" s="13">
         <v>555</v>
       </c>
-      <c r="BG1" s="12">
+      <c r="BG1" s="13">
         <v>556</v>
       </c>
-      <c r="BH1" s="12">
+      <c r="BH1" s="13">
         <v>557</v>
       </c>
-      <c r="BI1" s="12">
+      <c r="BI1" s="13">
         <v>558</v>
       </c>
-      <c r="BJ1" s="12">
+      <c r="BJ1" s="13">
         <v>560</v>
       </c>
-      <c r="BK1" s="12">
+      <c r="BK1" s="13">
         <v>570</v>
       </c>
-      <c r="BL1" s="12">
+      <c r="BL1" s="13">
         <v>580</v>
       </c>
-      <c r="BM1" s="12">
+      <c r="BM1" s="13">
         <v>590</v>
       </c>
-      <c r="BN1" s="12">
+      <c r="BN1" s="13">
         <v>590</v>
       </c>
-      <c r="BO1" s="12">
+      <c r="BO1" s="13">
         <v>591</v>
       </c>
-      <c r="BP1" s="12">
+      <c r="BP1" s="13">
         <v>592</v>
       </c>
-      <c r="BQ1" s="12">
+      <c r="BQ1" s="13">
         <v>593</v>
       </c>
-      <c r="BR1" s="12">
+      <c r="BR1" s="13">
         <v>594</v>
       </c>
-      <c r="BS1" s="12">
+      <c r="BS1" s="13">
         <v>595</v>
       </c>
-      <c r="BT1" s="12">
+      <c r="BT1" s="13">
         <v>596</v>
       </c>
-      <c r="BU1" s="12">
+      <c r="BU1" s="13">
         <v>597</v>
       </c>
-      <c r="BV1" s="12">
+      <c r="BV1" s="13">
         <v>598</v>
       </c>
-      <c r="BW1" s="12">
+      <c r="BW1" s="13">
+        <v>599</v>
+      </c>
+      <c r="BX1" s="13">
         <v>602</v>
       </c>
-      <c r="BX1" s="12">
+      <c r="BY1" s="13">
         <v>603</v>
       </c>
-      <c r="BY1" s="12">
+      <c r="BZ1" s="13">
         <v>604</v>
       </c>
-      <c r="BZ1" s="12">
+      <c r="CA1" s="13">
         <v>605</v>
       </c>
-      <c r="CA1" s="12">
+      <c r="CB1" s="13">
         <v>606</v>
       </c>
-      <c r="CB1" s="12">
+      <c r="CC1" s="13">
         <v>607</v>
       </c>
-      <c r="CC1" s="12">
+      <c r="CD1" s="13">
         <v>608</v>
       </c>
-      <c r="CD1" s="12">
+      <c r="CE1" s="13">
         <v>609</v>
       </c>
-      <c r="CE1" s="12">
+      <c r="CF1" s="13">
         <v>610</v>
       </c>
-      <c r="CF1" s="12">
+      <c r="CG1" s="13">
         <v>611</v>
       </c>
-      <c r="CG1" s="12">
+      <c r="CH1" s="13">
         <v>613</v>
       </c>
-      <c r="CH1" s="12">
+      <c r="CI1" s="13">
         <v>615</v>
       </c>
-      <c r="CI1" s="12">
+      <c r="CJ1" s="13">
         <v>624</v>
       </c>
-      <c r="CJ1" s="12">
+      <c r="CK1" s="13">
         <v>625</v>
       </c>
-      <c r="CK1" s="12">
+      <c r="CL1" s="13">
         <v>626</v>
       </c>
-      <c r="CL1" s="12">
+      <c r="CM1" s="13">
         <v>630</v>
       </c>
-      <c r="CM1" s="12">
+      <c r="CN1" s="13">
         <v>631</v>
       </c>
-      <c r="CN1" s="12">
+      <c r="CO1" s="13">
         <v>632</v>
       </c>
-      <c r="CO1" s="12">
+      <c r="CP1" s="13">
         <v>633</v>
       </c>
-      <c r="CP1" s="12">
+      <c r="CQ1" s="13">
         <v>634</v>
       </c>
-      <c r="CQ1" s="12">
+      <c r="CR1" s="13">
         <v>635</v>
       </c>
-      <c r="CR1" s="12">
+      <c r="CS1" s="13">
         <v>636</v>
       </c>
-      <c r="CS1" s="12">
+      <c r="CT1" s="13">
         <v>637</v>
       </c>
-      <c r="CT1" s="12">
+      <c r="CU1" s="13">
         <v>642</v>
       </c>
-      <c r="CU1" s="12">
+      <c r="CV1" s="13">
         <v>645</v>
       </c>
-      <c r="CV1" s="12">
+      <c r="CW1" s="13">
         <v>650</v>
       </c>
-      <c r="CW1" s="12">
+      <c r="CX1" s="13">
         <v>651</v>
       </c>
-      <c r="CX1" s="12">
+      <c r="CY1" s="13">
         <v>654</v>
       </c>
-      <c r="CY1" s="12">
+      <c r="CZ1" s="13">
         <v>655</v>
       </c>
-      <c r="CZ1" s="12">
+      <c r="DA1" s="13">
         <v>656</v>
       </c>
-      <c r="DA1" s="12">
+      <c r="DB1" s="13">
         <v>657</v>
       </c>
-      <c r="DB1" s="12">
+      <c r="DC1" s="13">
         <v>658</v>
       </c>
-      <c r="DC1" s="12">
+      <c r="DD1" s="13">
         <v>660</v>
       </c>
-      <c r="DD1" s="12">
+      <c r="DE1" s="13">
         <v>670</v>
       </c>
-      <c r="DE1" s="12">
+      <c r="DF1" s="13">
         <v>680</v>
       </c>
-      <c r="DF1" s="12">
+      <c r="DG1" s="13">
         <v>690</v>
       </c>
-      <c r="DG1" s="12">
+      <c r="DH1" s="13">
         <v>691</v>
       </c>
-      <c r="DH1" s="12">
+      <c r="DI1" s="13">
         <v>692</v>
       </c>
-      <c r="DI1" s="12">
+      <c r="DJ1" s="13">
         <v>693</v>
       </c>
-      <c r="DJ1" s="12">
+      <c r="DK1" s="13">
         <v>694</v>
       </c>
-      <c r="DK1" s="12">
+      <c r="DL1" s="13">
         <v>695</v>
       </c>
-      <c r="DL1" s="12">
+      <c r="DM1" s="13">
         <v>696</v>
       </c>
-      <c r="DM1" s="12">
+      <c r="DN1" s="13">
         <v>697</v>
       </c>
-      <c r="DN1" s="12">
+      <c r="DO1" s="13">
         <v>698</v>
       </c>
-      <c r="DO1" s="12">
+      <c r="DP1" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="DQ1" s="13">
         <v>995</v>
       </c>
-      <c r="DP1" s="12">
+      <c r="DR1" s="13">
         <v>996</v>
       </c>
-      <c r="DQ1" s="13">
+      <c r="DS1" s="13">
         <v>63</v>
       </c>
-      <c r="DR1" s="12">
+      <c r="DT1" s="13">
         <v>998</v>
       </c>
-      <c r="DS1" s="40" t="s">
+      <c r="DU1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="DT1" s="42" t="s">
+      <c r="DV1" s="42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+    <row r="2" spans="1:126" x14ac:dyDescent="0.15">
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -5918,359 +5975,365 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P2" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q2" s="12" t="s">
+      <c r="P2" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q2" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="U2" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="V2" s="12" t="s">
+      <c r="U2" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="V2" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AA2" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AB2" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AC2" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AD2" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AE2" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AF2" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="AG2" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="AH2" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="AI2" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ2" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="AL2" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="AN2" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="AO2" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="AP2" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="AQ2" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="AS2" s="13" t="s">
+        <v>985</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="AU2" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="AV2" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW2" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="AX2" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="AY2" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="BA2" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="BB2" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="BC2" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="BD2" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="BE2" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="BF2" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="BG2" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="BH2" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="BI2" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="BJ2" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="BK2" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="BL2" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="BM2" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="BN2" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="BO2" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="BP2" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="BQ2" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="BR2" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="BS2" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="BT2" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="BU2" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="BV2" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="BW2" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="BX2" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="BY2" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="BZ2" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="CA2" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB2" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="CC2" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="CD2" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="CE2" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="CF2" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="CG2" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="CH2" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="CI2" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="CJ2" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="CK2" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="CL2" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="AI2" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="AL2" s="12" t="s">
+      <c r="CM2" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="CN2" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="CO2" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="CP2" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="AP2" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="AQ2" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="AR2" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="AS2" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="AT2" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="AU2" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="AV2" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="AW2" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="AX2" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="AY2" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="AZ2" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="BA2" s="12" t="s">
+      <c r="CQ2" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="CR2" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="CS2" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="CT2" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="CU2" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="CV2" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="BB2" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="BC2" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="BD2" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="BE2" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="BF2" s="12" t="s">
+      <c r="CW2" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="CX2" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="CY2" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="CZ2" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="BG2" s="12" t="s">
+      <c r="DA2" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="BH2" s="12" t="s">
+      <c r="DB2" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="BI2" s="12" t="s">
+      <c r="DC2" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="BJ2" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="BK2" s="12" t="s">
+      <c r="DD2" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="DE2" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="BL2" s="12" t="s">
+      <c r="DF2" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="BM2" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="BN2" s="12" t="s">
+      <c r="DG2" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="BO2" s="12" t="s">
+      <c r="DH2" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="BP2" s="12" t="s">
+      <c r="DI2" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="BQ2" s="12" t="s">
+      <c r="DJ2" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="BR2" s="12" t="s">
+      <c r="DK2" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="DL2" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="BT2" s="12" t="s">
+      <c r="DM2" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="BU2" s="12" t="s">
+      <c r="DN2" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="BV2" s="12" t="s">
+      <c r="DO2" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="BW2" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="BX2" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="BY2" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="BZ2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="CA2" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="CB2" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="CC2" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="CD2" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="CE2" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="CF2" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="CG2" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="CH2" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="CI2" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="CJ2" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="CK2" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="CL2" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="CM2" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="CN2" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="CO2" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="CP2" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="CQ2" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="CR2" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="CS2" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="CT2" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="CU2" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="CV2" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="CW2" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="CX2" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="CY2" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="CZ2" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="DA2" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="DB2" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="DC2" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="DD2" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="DE2" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="DF2" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="DG2" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="DH2" s="12" t="s">
-        <v>429</v>
-      </c>
-      <c r="DI2" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="DJ2" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="DK2" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="DL2" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="DM2" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="DN2" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="DO2" s="12" t="s">
+      <c r="DP2" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="DQ2" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="DP2" s="12" t="s">
+      <c r="DR2" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="DQ2" s="13" t="s">
+      <c r="DS2" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="DR2" s="12" t="s">
+      <c r="DT2" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="DS2" s="41"/>
-      <c r="DT2" s="43"/>
+      <c r="DU2" s="41"/>
+      <c r="DV2" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="DS1:DS2"/>
-    <mergeCell ref="DT1:DT2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="DU1:DU2"/>
+    <mergeCell ref="DV1:DV2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6279,535 +6342,553 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FR2"/>
+  <dimension ref="A1:FX2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:174" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:180" x14ac:dyDescent="0.15">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12">
+      <c r="K1" s="13">
         <v>1</v>
       </c>
-      <c r="L1" s="12">
+      <c r="L1" s="13">
         <v>2</v>
       </c>
-      <c r="M1" s="12">
+      <c r="M1" s="13">
+        <v>3</v>
+      </c>
+      <c r="N1" s="13">
         <v>61</v>
       </c>
-      <c r="N1" s="12">
+      <c r="O1" s="13">
         <v>502</v>
       </c>
-      <c r="O1" s="12">
+      <c r="P1" s="13">
         <v>503</v>
       </c>
-      <c r="P1" s="12">
+      <c r="Q1" s="13">
         <v>504</v>
       </c>
-      <c r="Q1" s="12">
+      <c r="R1" s="13">
         <v>505</v>
       </c>
-      <c r="R1" s="12">
+      <c r="S1" s="13">
         <v>506</v>
       </c>
-      <c r="S1" s="12">
+      <c r="T1" s="13">
         <v>507</v>
       </c>
-      <c r="T1" s="12">
+      <c r="U1" s="13">
         <v>508</v>
       </c>
-      <c r="U1" s="12">
+      <c r="V1" s="13">
         <v>509</v>
       </c>
-      <c r="V1" s="12">
+      <c r="W1" s="13">
         <v>510</v>
       </c>
-      <c r="W1" s="12">
+      <c r="X1" s="13">
         <v>511</v>
       </c>
-      <c r="X1" s="12">
+      <c r="Y1" s="13">
         <v>513</v>
       </c>
-      <c r="Y1" s="12">
+      <c r="Z1" s="13">
         <v>515</v>
       </c>
-      <c r="Z1" s="12">
+      <c r="AA1" s="13">
         <v>516</v>
       </c>
-      <c r="AA1" s="12">
+      <c r="AB1" s="13">
         <v>517</v>
       </c>
-      <c r="AB1" s="12">
+      <c r="AC1" s="13">
         <v>518</v>
       </c>
-      <c r="AC1" s="12">
+      <c r="AD1" s="13">
         <v>519</v>
       </c>
-      <c r="AD1" s="12">
+      <c r="AE1" s="13">
         <v>520</v>
       </c>
-      <c r="AE1" s="12">
+      <c r="AF1" s="13">
         <v>521</v>
       </c>
-      <c r="AF1" s="12">
+      <c r="AG1" s="13">
         <v>522</v>
       </c>
-      <c r="AG1" s="12">
+      <c r="AH1" s="13">
         <v>523</v>
       </c>
-      <c r="AH1" s="12">
+      <c r="AI1" s="13">
         <v>524</v>
       </c>
-      <c r="AI1" s="12">
+      <c r="AJ1" s="13">
         <v>525</v>
       </c>
-      <c r="AJ1" s="12">
+      <c r="AK1" s="13">
         <v>526</v>
       </c>
-      <c r="AK1" s="12">
+      <c r="AL1" s="13">
         <v>527</v>
       </c>
-      <c r="AL1" s="12">
+      <c r="AM1" s="13">
         <v>528</v>
       </c>
-      <c r="AM1" s="12">
+      <c r="AN1" s="13">
         <v>529</v>
       </c>
-      <c r="AN1" s="12">
+      <c r="AO1" s="13">
         <v>530</v>
       </c>
-      <c r="AO1" s="12">
+      <c r="AP1" s="13">
         <v>531</v>
       </c>
-      <c r="AP1" s="12">
+      <c r="AQ1" s="13">
         <v>532</v>
       </c>
-      <c r="AQ1" s="12">
+      <c r="AR1" s="13">
         <v>533</v>
       </c>
-      <c r="AR1" s="12">
+      <c r="AS1" s="13">
         <v>534</v>
       </c>
-      <c r="AS1" s="12">
+      <c r="AT1" s="13">
         <v>535</v>
       </c>
-      <c r="AT1" s="12">
+      <c r="AU1" s="13">
         <v>536</v>
       </c>
-      <c r="AU1" s="12">
+      <c r="AV1" s="13">
         <v>537</v>
       </c>
-      <c r="AV1" s="12">
+      <c r="AW1" s="13">
         <v>538</v>
       </c>
-      <c r="AW1" s="12">
+      <c r="AX1" s="13">
         <v>539</v>
       </c>
-      <c r="AX1" s="12">
+      <c r="AY1" s="13">
         <v>540</v>
       </c>
-      <c r="AY1" s="12">
+      <c r="AZ1" s="13">
         <v>541</v>
       </c>
-      <c r="AZ1" s="12">
+      <c r="BA1" s="13">
         <v>542</v>
       </c>
-      <c r="BA1" s="12">
+      <c r="BB1" s="13">
         <v>543</v>
       </c>
-      <c r="BB1" s="12">
+      <c r="BC1" s="13">
         <v>544</v>
       </c>
-      <c r="BC1" s="12">
+      <c r="BD1" s="13">
         <v>545</v>
       </c>
-      <c r="BD1" s="12">
+      <c r="BE1" s="13">
+        <v>546</v>
+      </c>
+      <c r="BF1" s="13">
         <v>549</v>
       </c>
-      <c r="BE1" s="12">
-        <v>550</v>
-      </c>
-      <c r="BF1" s="12">
+      <c r="BG1" s="13">
         <v>551</v>
       </c>
-      <c r="BG1" s="12">
+      <c r="BH1" s="13">
         <v>554</v>
       </c>
-      <c r="BH1" s="12">
+      <c r="BI1" s="13">
         <v>555</v>
       </c>
-      <c r="BI1" s="12">
+      <c r="BJ1" s="13">
         <v>556</v>
       </c>
-      <c r="BJ1" s="12">
+      <c r="BK1" s="13">
         <v>557</v>
       </c>
-      <c r="BK1" s="12">
+      <c r="BL1" s="13">
         <v>558</v>
       </c>
-      <c r="BL1" s="12">
+      <c r="BM1" s="13">
         <v>560</v>
       </c>
-      <c r="BM1" s="12">
+      <c r="BN1" s="13">
         <v>570</v>
       </c>
-      <c r="BN1" s="12">
+      <c r="BO1" s="13">
         <v>580</v>
       </c>
-      <c r="BO1" s="12">
+      <c r="BP1" s="13">
         <v>590</v>
       </c>
-      <c r="BP1" s="12">
+      <c r="BQ1" s="13">
         <v>590</v>
       </c>
-      <c r="BQ1" s="12">
+      <c r="BR1" s="13">
         <v>591</v>
       </c>
-      <c r="BR1" s="12">
+      <c r="BS1" s="13">
         <v>592</v>
       </c>
-      <c r="BS1" s="12">
+      <c r="BT1" s="13">
         <v>593</v>
       </c>
-      <c r="BT1" s="12">
+      <c r="BU1" s="13">
         <v>594</v>
       </c>
-      <c r="BU1" s="12">
+      <c r="BV1" s="13">
         <v>595</v>
       </c>
-      <c r="BV1" s="12">
+      <c r="BW1" s="13">
         <v>596</v>
       </c>
-      <c r="BW1" s="12">
+      <c r="BX1" s="13">
         <v>597</v>
       </c>
-      <c r="BX1" s="12">
+      <c r="BY1" s="13">
         <v>598</v>
       </c>
-      <c r="BY1" s="12">
+      <c r="BZ1" s="13">
+        <v>599</v>
+      </c>
+      <c r="CA1" s="13">
         <v>602</v>
       </c>
-      <c r="BZ1" s="12">
+      <c r="CB1" s="13">
         <v>603</v>
       </c>
-      <c r="CA1" s="12">
+      <c r="CC1" s="13">
         <v>604</v>
       </c>
-      <c r="CB1" s="12">
+      <c r="CD1" s="13">
         <v>605</v>
       </c>
-      <c r="CC1" s="12">
+      <c r="CE1" s="13">
         <v>606</v>
       </c>
-      <c r="CD1" s="12">
+      <c r="CF1" s="13">
         <v>607</v>
       </c>
-      <c r="CE1" s="12">
+      <c r="CG1" s="13">
         <v>608</v>
       </c>
-      <c r="CF1" s="12">
+      <c r="CH1" s="13">
         <v>609</v>
       </c>
-      <c r="CG1" s="12">
+      <c r="CI1" s="13">
         <v>610</v>
       </c>
-      <c r="CH1" s="12">
+      <c r="CJ1" s="13">
         <v>611</v>
       </c>
-      <c r="CI1" s="12">
+      <c r="CK1" s="13">
         <v>613</v>
       </c>
-      <c r="CJ1" s="12">
+      <c r="CL1" s="13">
         <v>615</v>
       </c>
-      <c r="CK1" s="12">
+      <c r="CM1" s="13">
         <v>624</v>
       </c>
-      <c r="CL1" s="12">
+      <c r="CN1" s="13">
         <v>625</v>
       </c>
-      <c r="CM1" s="12">
+      <c r="CO1" s="13">
         <v>626</v>
       </c>
-      <c r="CN1" s="12">
+      <c r="CP1" s="13">
         <v>630</v>
       </c>
-      <c r="CO1" s="12">
+      <c r="CQ1" s="13">
         <v>631</v>
       </c>
-      <c r="CP1" s="12">
+      <c r="CR1" s="13">
         <v>632</v>
       </c>
-      <c r="CQ1" s="12">
+      <c r="CS1" s="13">
         <v>633</v>
       </c>
-      <c r="CR1" s="12">
+      <c r="CT1" s="13">
         <v>634</v>
       </c>
-      <c r="CS1" s="12">
+      <c r="CU1" s="13">
         <v>635</v>
       </c>
-      <c r="CT1" s="12">
+      <c r="CV1" s="13">
         <v>636</v>
       </c>
-      <c r="CU1" s="12">
+      <c r="CW1" s="13">
         <v>637</v>
       </c>
-      <c r="CV1" s="12">
+      <c r="CX1" s="13">
         <v>642</v>
       </c>
-      <c r="CW1" s="12">
+      <c r="CY1" s="13">
         <v>645</v>
       </c>
-      <c r="CX1" s="12">
+      <c r="CZ1" s="13">
         <v>650</v>
       </c>
-      <c r="CY1" s="12">
+      <c r="DA1" s="13">
         <v>651</v>
       </c>
-      <c r="CZ1" s="12">
+      <c r="DB1" s="13">
         <v>654</v>
       </c>
-      <c r="DA1" s="12">
+      <c r="DC1" s="13">
         <v>655</v>
       </c>
-      <c r="DB1" s="12">
+      <c r="DD1" s="13">
         <v>656</v>
       </c>
-      <c r="DC1" s="12">
+      <c r="DE1" s="13">
         <v>657</v>
       </c>
-      <c r="DD1" s="12">
+      <c r="DF1" s="13">
         <v>658</v>
       </c>
-      <c r="DE1" s="12">
+      <c r="DG1" s="13">
         <v>660</v>
       </c>
-      <c r="DF1" s="12">
+      <c r="DH1" s="13">
         <v>670</v>
       </c>
-      <c r="DG1" s="12">
+      <c r="DI1" s="13">
         <v>680</v>
       </c>
-      <c r="DH1" s="12">
+      <c r="DJ1" s="13">
         <v>690</v>
       </c>
-      <c r="DI1" s="12">
+      <c r="DK1" s="13">
         <v>691</v>
       </c>
-      <c r="DJ1" s="12">
+      <c r="DL1" s="13">
         <v>692</v>
       </c>
-      <c r="DK1" s="12">
+      <c r="DM1" s="13">
         <v>693</v>
       </c>
-      <c r="DL1" s="12">
+      <c r="DN1" s="13">
         <v>694</v>
       </c>
-      <c r="DM1" s="12">
+      <c r="DO1" s="13">
         <v>695</v>
       </c>
-      <c r="DN1" s="12">
+      <c r="DP1" s="13">
         <v>696</v>
       </c>
-      <c r="DO1" s="12">
+      <c r="DQ1" s="13">
         <v>697</v>
       </c>
-      <c r="DP1" s="12">
+      <c r="DR1" s="13">
         <v>698</v>
       </c>
-      <c r="DQ1" s="12">
+      <c r="DS1" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="DT1" s="13">
         <v>702</v>
       </c>
-      <c r="DR1" s="12">
+      <c r="DU1" s="13">
         <v>703</v>
       </c>
-      <c r="DS1" s="12">
+      <c r="DV1" s="13">
         <v>704</v>
       </c>
-      <c r="DT1" s="12">
+      <c r="DW1" s="13">
         <v>705</v>
       </c>
-      <c r="DU1" s="12">
+      <c r="DX1" s="13">
         <v>706</v>
       </c>
-      <c r="DV1" s="12">
+      <c r="DY1" s="13">
         <v>707</v>
       </c>
-      <c r="DW1" s="12">
+      <c r="DZ1" s="13">
         <v>708</v>
       </c>
-      <c r="DX1" s="12">
+      <c r="EA1" s="13">
         <v>709</v>
       </c>
-      <c r="DY1" s="12">
+      <c r="EB1" s="13">
         <v>710</v>
       </c>
-      <c r="DZ1" s="12">
+      <c r="EC1" s="13">
         <v>711</v>
       </c>
-      <c r="EA1" s="12">
+      <c r="ED1" s="13">
         <v>713</v>
       </c>
-      <c r="EB1" s="12">
+      <c r="EE1" s="13">
         <v>715</v>
       </c>
-      <c r="EC1" s="12">
+      <c r="EF1" s="13">
         <v>724</v>
       </c>
-      <c r="ED1" s="12">
+      <c r="EG1" s="13">
         <v>725</v>
       </c>
-      <c r="EE1" s="12">
+      <c r="EH1" s="13">
         <v>726</v>
       </c>
-      <c r="EF1" s="12">
+      <c r="EI1" s="13">
         <v>730</v>
       </c>
-      <c r="EG1" s="12">
+      <c r="EJ1" s="13">
         <v>731</v>
       </c>
-      <c r="EH1" s="12">
+      <c r="EK1" s="13">
         <v>732</v>
       </c>
-      <c r="EI1" s="12">
+      <c r="EL1" s="13">
         <v>733</v>
       </c>
-      <c r="EJ1" s="12">
+      <c r="EM1" s="13">
         <v>734</v>
       </c>
-      <c r="EK1" s="12">
+      <c r="EN1" s="13">
         <v>735</v>
       </c>
-      <c r="EL1" s="12">
+      <c r="EO1" s="13">
         <v>736</v>
       </c>
-      <c r="EM1" s="12">
+      <c r="EP1" s="13">
         <v>737</v>
       </c>
-      <c r="EN1" s="12">
+      <c r="EQ1" s="13">
         <v>742</v>
       </c>
-      <c r="EO1" s="12">
+      <c r="ER1" s="13">
         <v>745</v>
       </c>
-      <c r="EP1" s="12">
+      <c r="ES1" s="13">
         <v>750</v>
       </c>
-      <c r="EQ1" s="12">
+      <c r="ET1" s="13">
         <v>751</v>
       </c>
-      <c r="ER1" s="12">
+      <c r="EU1" s="13">
         <v>754</v>
       </c>
-      <c r="ES1" s="12">
+      <c r="EV1" s="13">
         <v>755</v>
       </c>
-      <c r="ET1" s="12">
+      <c r="EW1" s="13">
         <v>756</v>
       </c>
-      <c r="EU1" s="12">
+      <c r="EX1" s="13">
         <v>757</v>
       </c>
-      <c r="EV1" s="12">
+      <c r="EY1" s="13">
         <v>758</v>
       </c>
-      <c r="EW1" s="12">
+      <c r="EZ1" s="13">
         <v>760</v>
       </c>
-      <c r="EX1" s="12">
+      <c r="FA1" s="13" t="s">
+        <v>989</v>
+      </c>
+      <c r="FB1" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="FC1" s="13">
         <v>770</v>
       </c>
-      <c r="EY1" s="12">
+      <c r="FD1" s="13">
         <v>780</v>
       </c>
-      <c r="EZ1" s="12">
+      <c r="FE1" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="FF1" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="FG1" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="FH1" s="13">
         <v>790</v>
       </c>
-      <c r="FA1" s="12">
+      <c r="FI1" s="13">
         <v>791</v>
       </c>
-      <c r="FB1" s="12">
+      <c r="FJ1" s="13">
         <v>792</v>
       </c>
-      <c r="FC1" s="12">
+      <c r="FK1" s="13">
         <v>793</v>
       </c>
-      <c r="FD1" s="12">
+      <c r="FL1" s="13">
         <v>794</v>
       </c>
-      <c r="FE1" s="12">
+      <c r="FM1" s="13">
         <v>795</v>
       </c>
-      <c r="FF1" s="12">
+      <c r="FN1" s="13">
         <v>796</v>
       </c>
-      <c r="FG1" s="12">
+      <c r="FO1" s="13">
         <v>797</v>
       </c>
-      <c r="FH1" s="12">
+      <c r="FP1" s="13">
         <v>798</v>
       </c>
-      <c r="FI1" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="FJ1" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="FK1" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="FL1" s="12">
-        <v>995</v>
-      </c>
-      <c r="FM1" s="12">
-        <v>996</v>
-      </c>
-      <c r="FN1" s="12">
-        <v>997</v>
-      </c>
-      <c r="FO1" s="13">
+      <c r="FQ1" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="FR1" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="FS1" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="FT1" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="FU1" s="13">
         <v>63</v>
       </c>
-      <c r="FP1" s="12">
+      <c r="FV1" s="13">
         <v>998</v>
       </c>
-      <c r="FQ1" s="40" t="s">
+      <c r="FW1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="FR1" s="42" t="s">
+      <c r="FX1" s="42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:174" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+    <row r="2" spans="1:180" x14ac:dyDescent="0.15">
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -6817,509 +6898,527 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="N2" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="P2" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="Q2" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="R2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="T2" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="U2" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="V2" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="W2" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="W2" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="Y2" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Z2" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AA2" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AB2" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AC2" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AD2" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AE2" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AF2" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AG2" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AH2" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AI2" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="AJ2" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="AL2" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="AN2" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="AO2" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="AP2" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="AQ2" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="AS2" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="AU2" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="AV2" s="13" t="s">
+        <v>985</v>
+      </c>
+      <c r="AW2" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="AX2" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="AY2" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="BA2" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="BB2" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="BC2" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="BD2" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="BE2" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="BF2" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="BG2" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="BH2" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="BI2" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="BJ2" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="BK2" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="BL2" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="BM2" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="BN2" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="BO2" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="BP2" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="BQ2" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="BR2" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="BS2" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="BT2" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="BU2" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="BV2" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="BW2" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="BX2" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="BY2" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="BZ2" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="CA2" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="CB2" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="CC2" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="CD2" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="CE2" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="CF2" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="CG2" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="CH2" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="CI2" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="CJ2" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="CK2" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="CL2" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="CM2" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="CN2" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="CO2" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="AK2" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL2" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="AM2" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="AN2" s="12" t="s">
+      <c r="CP2" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="CQ2" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="AP2" s="12" t="s">
+      <c r="CR2" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="AQ2" s="12" t="s">
+      <c r="CS2" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="AR2" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="AS2" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="AT2" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="AU2" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="AV2" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="AW2" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="AX2" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="AY2" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="AZ2" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="BA2" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="BB2" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="BC2" s="12" t="s">
+      <c r="CT2" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="CU2" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="CV2" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="CW2" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="CX2" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="CY2" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="BD2" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="BE2" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="BF2" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="BG2" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="BH2" s="12" t="s">
+      <c r="CZ2" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="DA2" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="DB2" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="DC2" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="BI2" s="12" t="s">
+      <c r="DD2" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="BJ2" s="12" t="s">
+      <c r="DE2" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="BK2" s="12" t="s">
+      <c r="DF2" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="BL2" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="BM2" s="12" t="s">
+      <c r="DG2" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="DH2" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="BN2" s="12" t="s">
+      <c r="DI2" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="BO2" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="BP2" s="12" t="s">
+      <c r="DJ2" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="BQ2" s="12" t="s">
+      <c r="DK2" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="BR2" s="12" t="s">
+      <c r="DL2" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="DM2" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="BT2" s="12" t="s">
+      <c r="DN2" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="BU2" s="12" t="s">
+      <c r="DO2" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="BV2" s="12" t="s">
+      <c r="DP2" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="BW2" s="12" t="s">
+      <c r="DQ2" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="BX2" s="12" t="s">
+      <c r="DR2" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="BY2" s="12" t="s">
+      <c r="DS2" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="DT2" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="BZ2" s="12" t="s">
+      <c r="DU2" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="CA2" s="12" t="s">
+      <c r="DV2" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="CB2" s="12" t="s">
+      <c r="DW2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="CC2" s="12" t="s">
+      <c r="DX2" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="CD2" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="CE2" s="12" t="s">
+      <c r="DY2" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="DZ2" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="CF2" s="12" t="s">
+      <c r="EA2" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="CG2" s="12" t="s">
+      <c r="EB2" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="CH2" s="12" t="s">
+      <c r="EC2" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="CI2" s="12" t="s">
+      <c r="ED2" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="CJ2" s="12" t="s">
+      <c r="EE2" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="CK2" s="12" t="s">
+      <c r="EF2" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="CL2" s="12" t="s">
+      <c r="EG2" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="CM2" s="12" t="s">
+      <c r="EH2" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="CN2" s="12" t="s">
+      <c r="EI2" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="CO2" s="12" t="s">
+      <c r="EJ2" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="CP2" s="12" t="s">
+      <c r="EK2" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="CQ2" s="12" t="s">
+      <c r="EL2" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="CR2" s="12" t="s">
+      <c r="EM2" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="CS2" s="12" t="s">
+      <c r="EN2" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="CT2" s="12" t="s">
+      <c r="EO2" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="CU2" s="12" t="s">
+      <c r="EP2" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="CV2" s="12" t="s">
+      <c r="EQ2" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="CW2" s="12" t="s">
+      <c r="ER2" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="CX2" s="12" t="s">
+      <c r="ES2" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="CY2" s="12" t="s">
+      <c r="ET2" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="CZ2" s="12" t="s">
+      <c r="EU2" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="DA2" s="12" t="s">
+      <c r="EV2" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="DB2" s="12" t="s">
+      <c r="EW2" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="DC2" s="12" t="s">
+      <c r="EX2" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="DD2" s="12" t="s">
+      <c r="EY2" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="DE2" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="DF2" s="12" t="s">
+      <c r="EZ2" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="FA2" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="FB2" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="FC2" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="DG2" s="12" t="s">
+      <c r="FD2" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="DH2" s="12" t="s">
+      <c r="FE2" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="FF2" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="FG2" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="FH2" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="DI2" s="12" t="s">
+      <c r="FI2" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="DJ2" s="12" t="s">
+      <c r="FJ2" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="DK2" s="12" t="s">
+      <c r="FK2" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="DL2" s="12" t="s">
+      <c r="FL2" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="DM2" s="12" t="s">
+      <c r="FM2" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="DN2" s="12" t="s">
+      <c r="FN2" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="DO2" s="12" t="s">
+      <c r="FO2" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="DP2" s="12" t="s">
+      <c r="FP2" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="DQ2" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="DR2" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="DS2" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="DT2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="DU2" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="DV2" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="DW2" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="DX2" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="DY2" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="DZ2" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="EA2" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="EB2" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="EC2" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="ED2" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="EE2" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="EF2" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="EG2" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="EH2" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="EI2" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="EJ2" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="EK2" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="EL2" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="EM2" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="EN2" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="EO2" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="EP2" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="EQ2" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="ER2" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="ES2" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="ET2" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="EU2" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="EV2" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="EW2" s="12" t="s">
-        <v>456</v>
-      </c>
-      <c r="EX2" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="EY2" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="EZ2" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="FA2" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="FB2" s="12" t="s">
-        <v>429</v>
-      </c>
-      <c r="FC2" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="FD2" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="FE2" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="FF2" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="FG2" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="FH2" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="FI2" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="FJ2" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="FK2" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="FL2" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="FM2" s="12" t="s">
+      <c r="FQ2" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="FR2" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="FN2" s="12" t="s">
+      <c r="FS2" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="FT2" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="FO2" s="13" t="s">
+      <c r="FU2" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="FP2" s="12" t="s">
+      <c r="FV2" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="FQ2" s="41"/>
-      <c r="FR2" s="43"/>
+      <c r="FW2" s="41"/>
+      <c r="FX2" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="FQ1:FQ2"/>
-    <mergeCell ref="FR1:FR2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="FW1:FW2"/>
+    <mergeCell ref="FX1:FX2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7332,34 +7431,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:64" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -7526,7 +7625,7 @@
       </c>
     </row>
     <row r="2" spans="1:64" ht="51" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -7697,6 +7796,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="BK1:BK2"/>
     <mergeCell ref="BL1:BL2"/>
     <mergeCell ref="F1:F2"/>
@@ -7704,11 +7808,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7722,34 +7821,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -8006,7 +8105,7 @@
       </c>
     </row>
     <row r="2" spans="1:94" ht="51" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -8267,6 +8366,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="CO1:CO2"/>
     <mergeCell ref="CP1:CP2"/>
     <mergeCell ref="F1:F2"/>
@@ -8274,11 +8378,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8291,34 +8390,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:127" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -8674,7 +8773,7 @@
       </c>
     </row>
     <row r="2" spans="1:127" ht="51" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -9034,6 +9133,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="DV1:DV2"/>
     <mergeCell ref="DW1:DW2"/>
     <mergeCell ref="F1:F2"/>
@@ -9041,11 +9145,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9058,34 +9157,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:87" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -9321,7 +9420,7 @@
       </c>
     </row>
     <row r="2" spans="1:87" ht="51" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -9561,6 +9660,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="CH1:CH2"/>
     <mergeCell ref="CI1:CI2"/>
     <mergeCell ref="F1:F2"/>
@@ -9568,11 +9672,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9589,34 +9688,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -9801,7 +9900,7 @@
       </c>
     </row>
     <row r="2" spans="1:70" ht="63.75" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -9993,6 +10092,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="BQ1:BQ2"/>
     <mergeCell ref="BR1:BR2"/>
     <mergeCell ref="F1:F2"/>
@@ -10000,11 +10104,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10036,34 +10135,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:79" s="27" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -10267,15 +10366,15 @@
       <c r="BY1" s="5">
         <v>69</v>
       </c>
-      <c r="BZ1" s="33" t="s">
+      <c r="BZ1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="CA1" s="35" t="s">
+      <c r="CA1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:79" s="28" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -10486,7 +10585,7 @@
       <c r="BY2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BZ2" s="34"/>
+      <c r="BZ2" s="30"/>
       <c r="CA2" s="32"/>
     </row>
     <row r="3" spans="1:79" x14ac:dyDescent="0.15">
@@ -10516,6 +10615,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="BZ1:BZ2"/>
     <mergeCell ref="CA1:CA2"/>
     <mergeCell ref="F1:F2"/>
@@ -10523,11 +10627,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10540,34 +10639,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:80" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -10782,7 +10881,7 @@
       </c>
     </row>
     <row r="2" spans="1:80" ht="63.75" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -11001,6 +11100,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="CA1:CA2"/>
     <mergeCell ref="CB1:CB2"/>
     <mergeCell ref="F1:F2"/>
@@ -11008,11 +11112,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11025,34 +11124,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:242" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -11753,7 +11852,7 @@
       </c>
     </row>
     <row r="2" spans="1:242" ht="63.75" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -12458,6 +12557,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="IG1:IG2"/>
     <mergeCell ref="IH1:IH2"/>
     <mergeCell ref="F1:F2"/>
@@ -12465,11 +12569,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12482,34 +12581,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:282" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -13330,7 +13429,7 @@
       </c>
     </row>
     <row r="2" spans="1:282" ht="63.75" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -14155,6 +14254,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="JU1:JU2"/>
     <mergeCell ref="JV1:JV2"/>
     <mergeCell ref="F1:F2"/>
@@ -14162,11 +14266,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14179,34 +14278,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:318" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -15135,7 +15234,7 @@
       </c>
     </row>
     <row r="2" spans="1:318" ht="63.75" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -16068,6 +16167,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="LE1:LE2"/>
     <mergeCell ref="LF1:LF2"/>
     <mergeCell ref="F1:F2"/>
@@ -16075,11 +16179,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16092,34 +16191,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:144" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -16526,7 +16625,7 @@
       </c>
     </row>
     <row r="2" spans="1:144" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -16935,6 +17034,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="EM1:EM2"/>
     <mergeCell ref="EN1:EN2"/>
     <mergeCell ref="F1:F2"/>
@@ -16942,11 +17046,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16959,34 +17058,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:152" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -17417,7 +17516,7 @@
       </c>
     </row>
     <row r="2" spans="1:152" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -17850,6 +17949,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="EU1:EU2"/>
     <mergeCell ref="EV1:EV2"/>
     <mergeCell ref="F1:F2"/>
@@ -17857,11 +17961,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17874,34 +17973,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:214" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -18518,7 +18617,7 @@
       </c>
     </row>
     <row r="2" spans="1:214" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -19161,34 +19260,34 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:275" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -19988,7 +20087,7 @@
       </c>
     </row>
     <row r="2" spans="1:275" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -20819,31 +20918,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="46" t="s">
@@ -20944,7 +21043,7 @@
       </c>
     </row>
     <row r="2" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -20953,7 +21052,7 @@
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="34"/>
+      <c r="J2" s="30"/>
       <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
@@ -21046,6 +21145,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AO1:AO2"/>
     <mergeCell ref="F1:F2"/>
@@ -21053,11 +21157,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21091,34 +21190,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -21484,15 +21583,15 @@
       <c r="EA1" s="5">
         <v>123</v>
       </c>
-      <c r="EB1" s="33" t="s">
+      <c r="EB1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="EC1" s="35" t="s">
+      <c r="EC1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:133" s="26" customFormat="1" ht="60.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -21865,11 +21964,16 @@
       <c r="EA2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="EB2" s="34"/>
+      <c r="EB2" s="30"/>
       <c r="EC2" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="EB1:EB2"/>
     <mergeCell ref="EC1:EC2"/>
     <mergeCell ref="F1:F2"/>
@@ -21877,11 +21981,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21918,34 +22017,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -22083,15 +22182,15 @@
       <c r="BC1" s="5">
         <v>147</v>
       </c>
-      <c r="BD1" s="33" t="s">
+      <c r="BD1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="BE1" s="35" t="s">
+      <c r="BE1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:57" ht="63.75" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -22236,11 +22335,16 @@
       <c r="BC2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="BD2" s="34"/>
+      <c r="BD2" s="30"/>
       <c r="BE2" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="BD1:BD2"/>
     <mergeCell ref="BE1:BE2"/>
     <mergeCell ref="F1:F2"/>
@@ -22248,11 +22352,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22285,34 +22384,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:68" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -22483,15 +22582,15 @@
       <c r="BN1" s="5">
         <v>214</v>
       </c>
-      <c r="BO1" s="33" t="s">
+      <c r="BO1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="BP1" s="35" t="s">
+      <c r="BP1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:68" s="22" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -22669,11 +22768,16 @@
       <c r="BN2" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="BO2" s="34"/>
+      <c r="BO2" s="30"/>
       <c r="BP2" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="BO1:BO2"/>
     <mergeCell ref="BP1:BP2"/>
     <mergeCell ref="F1:F2"/>
@@ -22681,11 +22785,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22721,34 +22820,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:185" s="17" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -23270,15 +23369,15 @@
       <c r="GA1" s="5">
         <v>999</v>
       </c>
-      <c r="GB1" s="33" t="s">
+      <c r="GB1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="GC1" s="35" t="s">
+      <c r="GC1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:185" s="18" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -23812,6 +23911,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="GB1:GB2"/>
     <mergeCell ref="GC1:GC2"/>
     <mergeCell ref="F1:F2"/>
@@ -23819,11 +23923,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23859,34 +23958,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:238" s="17" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -24567,15 +24666,15 @@
       <c r="IB1" s="5">
         <v>999</v>
       </c>
-      <c r="IC1" s="33" t="s">
+      <c r="IC1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="ID1" s="35" t="s">
+      <c r="ID1" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:238" s="18" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -25268,6 +25367,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="IC1:IC2"/>
     <mergeCell ref="ID1:ID2"/>
     <mergeCell ref="F1:F2"/>
@@ -25275,11 +25379,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25309,34 +25408,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5">
@@ -25537,7 +25636,7 @@
       <c r="BX1" s="5">
         <v>63</v>
       </c>
-      <c r="BY1" s="33" t="s">
+      <c r="BY1" s="29" t="s">
         <v>10</v>
       </c>
       <c r="BZ1" s="38" t="s">
@@ -25545,7 +25644,7 @@
       </c>
     </row>
     <row r="2" spans="1:78" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -25758,6 +25857,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="BY1:BY2"/>
     <mergeCell ref="BZ1:BZ2"/>
     <mergeCell ref="F1:F2"/>
@@ -25765,11 +25869,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25800,34 +25899,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="12">
@@ -26040,7 +26139,7 @@
       <c r="CB1" s="16"/>
     </row>
     <row r="2" spans="1:80" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -26257,6 +26356,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="BZ1:BZ2"/>
     <mergeCell ref="CA1:CA2"/>
     <mergeCell ref="F1:F2"/>
@@ -26264,11 +26368,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
